--- a/data/trans_bre/IP1010-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,0</t>
+          <t>-3,48; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>-3,8; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,0</t>
+          <t>-4,01; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,0</t>
+          <t>-5,44; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,65</t>
+          <t>-1,12; 0,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,0</t>
+          <t>-2,41; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-2,76; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,86</t>
+          <t>-0,99; 1,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,38</t>
+          <t>-2,37; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,58</t>
+          <t>-5,16; 1,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,59</t>
+          <t>-1,75; 5,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,08</t>
+          <t>-1,04; 0,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,46</t>
+          <t>-0,59; 0,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; -0,13</t>
+          <t>-1,24; -0,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,57</t>
+          <t>-100,0; 159,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 641,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,0</t>
+          <t>-3,47; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,0</t>
+          <t>-3,01; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,0</t>
+          <t>-3,95; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,64</t>
+          <t>-1,08; 0,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,0</t>
+          <t>-1,87; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,0</t>
+          <t>-2,58; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,0</t>
+          <t>-3,02; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,83</t>
+          <t>-0,99; 1,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,66</t>
+          <t>-2,36; 0,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,58</t>
+          <t>-5,13; 1,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,66</t>
+          <t>-1,75; 5,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,27 +1114,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,1</t>
+          <t>-1,06; 0,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,53</t>
+          <t>-0,58; 0,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,14</t>
+          <t>-1,22; -0,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 159,29</t>
+          <t>-100,0; 171,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 641,41</t>
+          <t>-100,0; 609,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP1010-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Clase-trans_bre.xlsx
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,0</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,0</t>
+          <t>-3,61; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>-5,62; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,64</t>
+          <t>-1,11; 0,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,0</t>
+          <t>-2,4; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,0</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,82</t>
+          <t>-1,0; 1,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,7</t>
+          <t>-2,72; 0,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,53</t>
+          <t>-4,42; 1,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,62</t>
+          <t>-1,76; 5,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,1</t>
+          <t>-1,07; 0,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,49</t>
+          <t>-0,56; 0,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; -0,14</t>
+          <t>-1,15; -0,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 171,35</t>
+          <t>-100,0; 102,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 609,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1010-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1010-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,129 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.6901057836917844</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,47; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.465146080782981</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,76; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,91</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.7468854402683089</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4775534463289701</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.7255723987548311</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.764658076334997</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.611548776424966</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,62; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.911058712373044</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +733,127 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,92%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9632549988744114</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,11; 0,65</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,06; 0,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-5.620382200123599</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-58,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,65; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,0; 1,86</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,72; 0,38</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.03920682982539105</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5795003965389485</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.6891611256083641</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1092338667044523</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-53,17%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.108041320533655</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.063269663978252</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.401241440602088</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 1,58</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-1,76; 5,59</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6516089829030262</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +861,211 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-66,51%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-16,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-87,22%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.5502382787555865</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1089971562556976</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.5478796135436766</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.221759854954029</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.5875218992081666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,07; 0,08</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,56; 0,46</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; -0,13</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 102,57</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; inf</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.651591623819094</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.9963005599114939</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.721178083340198</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.863242321909272</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3839106629758364</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-0.917853433546322</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.5283807764822852</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.5317288491526845</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.6046372413854569</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.424965640460308</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-1.763046112327646</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1.575591207310503</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>5.587803558051864</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.3877151348958174</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.06053504746249064</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5323634272002337</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.6651456734390259</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1630505345489297</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.8721875109441252</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.07019012872382</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.5620941506478998</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.152593075019679</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.07925444681986707</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.4561379289362056</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-0.1281270060533975</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1.025721715055314</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1074,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
